--- a/05_Figures/HRvLR/F3_People/c_data/f3_people.xlsx
+++ b/05_Figures/HRvLR/F3_People/c_data/f3_people.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11924" uniqueCount="4098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11957" uniqueCount="4119">
   <si>
     <t>sheet</t>
   </si>
@@ -303,7 +303,7 @@
     <t>best single feature per task</t>
   </si>
   <si>
-    <t>02_HRvLR_groups/06_Classification/01_Proteins/c_data/protein_classification.xlsx</t>
+    <t>03_Group_comparisons/HRvLR/05_Classification/01_Proteins/c_data/protein_classification.xlsx</t>
   </si>
   <si>
     <t>auc, counts</t>
@@ -318,7 +318,7 @@
     <t>group difference against continuous interaction</t>
   </si>
   <si>
-    <t>02_HRvLR_groups/07_Trait_Associations/c_data/trait_associations.xlsx</t>
+    <t>03_Group_comparisons/HRvLR/06_Trait_Associations/c_data/trait_associations.xlsx</t>
   </si>
   <si>
     <t>group_difference; interaction</t>
@@ -11886,25 +11886,25 @@
     <t>LR_S30</t>
   </si>
   <si>
-    <t>b01ac1f6d6d70cf871c6751d533234fd</t>
-  </si>
-  <si>
-    <t>02_HRvLR_groups/06_Classification/02_Sets/c_data/set_classification.xlsx</t>
-  </si>
-  <si>
-    <t>2d5c57240ac4c245f6b3ae6409d38693</t>
-  </si>
-  <si>
-    <t>02_HRvLR_groups/06_Classification/03_Modules/c_data/module_classification.xlsx</t>
-  </si>
-  <si>
-    <t>3160dbe9810c780b4924a19c1e8f2f4f</t>
+    <t>a95402d461edffdb1bfe52e24fa7f7f5</t>
+  </si>
+  <si>
+    <t>03_Group_comparisons/HRvLR/05_Classification/02_Sets/c_data/set_classification.xlsx</t>
+  </si>
+  <si>
+    <t>b178395b3633ca781c3d08c789b73be2</t>
+  </si>
+  <si>
+    <t>03_Group_comparisons/HRvLR/05_Classification/03_Modules/c_data/module_classification.xlsx</t>
+  </si>
+  <si>
+    <t>40af5ef3d827e7eda16199768c84b50c</t>
   </si>
   <si>
     <t>associate</t>
   </si>
   <si>
-    <t>9ac893e6ae1926d745c3c47a1bb5b588</t>
+    <t>22366981c91de546cdab366e3b1baab4</t>
   </si>
   <si>
     <t>continuous</t>
@@ -11913,7 +11913,7 @@
     <t>04_Continuous_no_group/01_Trait_Associations/01_Proteins/c_data/protein_trait_associations.xlsx</t>
   </si>
   <si>
-    <t>400e71a7f9b28b71965d7d0a160d06c9</t>
+    <t>4c94a3c340f52458c17e5a5394bde99d</t>
   </si>
   <si>
     <t>corrected</t>
@@ -11928,7 +11928,7 @@
     <t>phenotype</t>
   </si>
   <si>
-    <t>00_Input/phenotype.csv</t>
+    <t>00_Setup/Input/phenotype.csv</t>
   </si>
   <si>
     <t>5a1989db406daa0b70189a9f0df52cf3</t>
@@ -12036,12 +12036,24 @@
     <t>1.2.1</t>
   </si>
   <si>
+    <t>evaluate</t>
+  </si>
+  <si>
+    <t>1.0.5</t>
+  </si>
+  <si>
     <t>farver</t>
   </si>
   <si>
     <t>2.1.2</t>
   </si>
   <si>
+    <t>fastmap</t>
+  </si>
+  <si>
+    <t>1.2.0</t>
+  </si>
+  <si>
     <t>foreach</t>
   </si>
   <si>
@@ -12105,6 +12117,18 @@
     <t>1.1.4</t>
   </si>
   <si>
+    <t>htmltools</t>
+  </si>
+  <si>
+    <t>0.5.9</t>
+  </si>
+  <si>
+    <t>htmlwidgets</t>
+  </si>
+  <si>
+    <t>1.6.4</t>
+  </si>
+  <si>
     <t>IRanges</t>
   </si>
   <si>
@@ -12117,6 +12141,18 @@
     <t>1.0.14</t>
   </si>
   <si>
+    <t>jsonlite</t>
+  </si>
+  <si>
+    <t>2.0.0</t>
+  </si>
+  <si>
+    <t>knitr</t>
+  </si>
+  <si>
+    <t>1.51</t>
+  </si>
+  <si>
     <t>labeling</t>
   </si>
   <si>
@@ -12132,9 +12168,6 @@
     <t>lifecycle</t>
   </si>
   <si>
-    <t>1.0.5</t>
-  </si>
-  <si>
     <t>magrittr</t>
   </si>
   <si>
@@ -12165,6 +12198,12 @@
     <t>3.1-169</t>
   </si>
   <si>
+    <t>otel</t>
+  </si>
+  <si>
+    <t>0.2.0</t>
+  </si>
+  <si>
     <t>patchwork</t>
   </si>
   <si>
@@ -12246,6 +12285,12 @@
     <t>CRAN (R 4.6.1)</t>
   </si>
   <si>
+    <t>rmarkdown</t>
+  </si>
+  <si>
+    <t>2.31</t>
+  </si>
+  <si>
     <t>rprojroot</t>
   </si>
   <si>
@@ -12312,6 +12357,12 @@
     <t>0.5.0</t>
   </si>
   <si>
+    <t>utf8</t>
+  </si>
+  <si>
+    <t>1.2.6</t>
+  </si>
+  <si>
     <t>vctrs</t>
   </si>
   <si>
@@ -12328,6 +12379,18 @@
   </si>
   <si>
     <t>3.0.2</t>
+  </si>
+  <si>
+    <t>xfun</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>yaml</t>
+  </si>
+  <si>
+    <t>2.3.12</t>
   </si>
 </sst>
 </file>
@@ -101862,7 +101925,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -102134,7 +102197,7 @@
         <v>4014</v>
       </c>
       <c r="B25" t="s">
-        <v>4005</v>
+        <v>4015</v>
       </c>
       <c r="C25" t="s">
         <v>3971</v>
@@ -102142,10 +102205,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>4015</v>
+        <v>4016</v>
       </c>
       <c r="B26" t="s">
-        <v>4016</v>
+        <v>4017</v>
       </c>
       <c r="C26" t="s">
         <v>3971</v>
@@ -102153,10 +102216,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>4017</v>
+        <v>4018</v>
       </c>
       <c r="B27" t="s">
-        <v>4018</v>
+        <v>4009</v>
       </c>
       <c r="C27" t="s">
         <v>3971</v>
@@ -102192,7 +102255,7 @@
         <v>4024</v>
       </c>
       <c r="C30" t="s">
-        <v>3968</v>
+        <v>3971</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -102236,7 +102299,7 @@
         <v>4032</v>
       </c>
       <c r="C34" t="s">
-        <v>3971</v>
+        <v>3968</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -102299,7 +102362,7 @@
         <v>4043</v>
       </c>
       <c r="B40" t="s">
-        <v>4044</v>
+        <v>4001</v>
       </c>
       <c r="C40" t="s">
         <v>3971</v>
@@ -102307,10 +102370,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
+        <v>4044</v>
+      </c>
+      <c r="B41" t="s">
         <v>4045</v>
-      </c>
-      <c r="B41" t="s">
-        <v>4046</v>
       </c>
       <c r="C41" t="s">
         <v>3971</v>
@@ -102318,10 +102381,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
+        <v>4046</v>
+      </c>
+      <c r="B42" t="s">
         <v>4047</v>
-      </c>
-      <c r="B42" t="s">
-        <v>4048</v>
       </c>
       <c r="C42" t="s">
         <v>3971</v>
@@ -102329,10 +102392,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
+        <v>4048</v>
+      </c>
+      <c r="B43" t="s">
         <v>4049</v>
-      </c>
-      <c r="B43" t="s">
-        <v>4050</v>
       </c>
       <c r="C43" t="s">
         <v>3971</v>
@@ -102340,10 +102403,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
+        <v>4050</v>
+      </c>
+      <c r="B44" t="s">
         <v>4051</v>
-      </c>
-      <c r="B44" t="s">
-        <v>4052</v>
       </c>
       <c r="C44" t="s">
         <v>3971</v>
@@ -102351,10 +102414,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
+        <v>4052</v>
+      </c>
+      <c r="B45" t="s">
         <v>4053</v>
-      </c>
-      <c r="B45" t="s">
-        <v>4054</v>
       </c>
       <c r="C45" t="s">
         <v>3971</v>
@@ -102362,10 +102425,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
+        <v>4054</v>
+      </c>
+      <c r="B46" t="s">
         <v>4055</v>
-      </c>
-      <c r="B46" t="s">
-        <v>4056</v>
       </c>
       <c r="C46" t="s">
         <v>3971</v>
@@ -102373,10 +102436,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
+        <v>4056</v>
+      </c>
+      <c r="B47" t="s">
         <v>4057</v>
-      </c>
-      <c r="B47" t="s">
-        <v>4058</v>
       </c>
       <c r="C47" t="s">
         <v>3971</v>
@@ -102384,10 +102447,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
+        <v>4058</v>
+      </c>
+      <c r="B48" t="s">
         <v>4059</v>
-      </c>
-      <c r="B48" t="s">
-        <v>4060</v>
       </c>
       <c r="C48" t="s">
         <v>3971</v>
@@ -102395,10 +102458,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
+        <v>4060</v>
+      </c>
+      <c r="B49" t="s">
         <v>4061</v>
-      </c>
-      <c r="B49" t="s">
-        <v>4062</v>
       </c>
       <c r="C49" t="s">
         <v>3971</v>
@@ -102406,10 +102469,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
+        <v>4062</v>
+      </c>
+      <c r="B50" t="s">
         <v>4063</v>
-      </c>
-      <c r="B50" t="s">
-        <v>4064</v>
       </c>
       <c r="C50" t="s">
         <v>3971</v>
@@ -102417,10 +102480,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
+        <v>4064</v>
+      </c>
+      <c r="B51" t="s">
         <v>4065</v>
-      </c>
-      <c r="B51" t="s">
-        <v>4066</v>
       </c>
       <c r="C51" t="s">
         <v>3971</v>
@@ -102428,21 +102491,21 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
+        <v>4066</v>
+      </c>
+      <c r="B52" t="s">
         <v>4067</v>
       </c>
-      <c r="B52" t="s">
-        <v>4068</v>
-      </c>
       <c r="C52" t="s">
-        <v>4069</v>
+        <v>3971</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>4070</v>
+        <v>4068</v>
       </c>
       <c r="B53" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="C53" t="s">
         <v>3971</v>
@@ -102450,21 +102513,21 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="B54" t="s">
-        <v>4073</v>
+        <v>4071</v>
       </c>
       <c r="C54" t="s">
-        <v>3968</v>
+        <v>3971</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>4074</v>
+        <v>4072</v>
       </c>
       <c r="B55" t="s">
-        <v>4075</v>
+        <v>4073</v>
       </c>
       <c r="C55" t="s">
         <v>3971</v>
@@ -102472,10 +102535,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>4076</v>
+        <v>4074</v>
       </c>
       <c r="B56" t="s">
-        <v>4077</v>
+        <v>4075</v>
       </c>
       <c r="C56" t="s">
         <v>3971</v>
@@ -102483,10 +102546,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>4078</v>
+        <v>4076</v>
       </c>
       <c r="B57" t="s">
-        <v>4079</v>
+        <v>4077</v>
       </c>
       <c r="C57" t="s">
         <v>3971</v>
@@ -102494,10 +102557,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>4080</v>
+        <v>4078</v>
       </c>
       <c r="B58" t="s">
-        <v>4081</v>
+        <v>4079</v>
       </c>
       <c r="C58" t="s">
         <v>3971</v>
@@ -102505,21 +102568,21 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
+        <v>4080</v>
+      </c>
+      <c r="B59" t="s">
+        <v>4081</v>
+      </c>
+      <c r="C59" t="s">
         <v>4082</v>
-      </c>
-      <c r="B59" t="s">
-        <v>4083</v>
-      </c>
-      <c r="C59" t="s">
-        <v>3971</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
+        <v>4083</v>
+      </c>
+      <c r="B60" t="s">
         <v>4084</v>
-      </c>
-      <c r="B60" t="s">
-        <v>4085</v>
       </c>
       <c r="C60" t="s">
         <v>3971</v>
@@ -102527,10 +102590,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
+        <v>4085</v>
+      </c>
+      <c r="B61" t="s">
         <v>4086</v>
-      </c>
-      <c r="B61" t="s">
-        <v>4087</v>
       </c>
       <c r="C61" t="s">
         <v>3971</v>
@@ -102538,13 +102601,13 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
+        <v>4087</v>
+      </c>
+      <c r="B62" t="s">
         <v>4088</v>
       </c>
-      <c r="B62" t="s">
-        <v>4044</v>
-      </c>
       <c r="C62" t="s">
-        <v>3971</v>
+        <v>3968</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -102552,7 +102615,7 @@
         <v>4089</v>
       </c>
       <c r="B63" t="s">
-        <v>3999</v>
+        <v>4090</v>
       </c>
       <c r="C63" t="s">
         <v>3971</v>
@@ -102560,10 +102623,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>4090</v>
+        <v>4091</v>
       </c>
       <c r="B64" t="s">
-        <v>4091</v>
+        <v>4092</v>
       </c>
       <c r="C64" t="s">
         <v>3971</v>
@@ -102571,10 +102634,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>4092</v>
+        <v>4093</v>
       </c>
       <c r="B65" t="s">
-        <v>4093</v>
+        <v>4094</v>
       </c>
       <c r="C65" t="s">
         <v>3971</v>
@@ -102582,10 +102645,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>4094</v>
+        <v>4095</v>
       </c>
       <c r="B66" t="s">
-        <v>4095</v>
+        <v>4096</v>
       </c>
       <c r="C66" t="s">
         <v>3971</v>
@@ -102593,12 +102656,133 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>4096</v>
+        <v>4097</v>
       </c>
       <c r="B67" t="s">
-        <v>4097</v>
+        <v>4098</v>
       </c>
       <c r="C67" t="s">
+        <v>3971</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>4099</v>
+      </c>
+      <c r="B68" t="s">
+        <v>4100</v>
+      </c>
+      <c r="C68" t="s">
+        <v>3971</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>4101</v>
+      </c>
+      <c r="B69" t="s">
+        <v>4102</v>
+      </c>
+      <c r="C69" t="s">
+        <v>3971</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>4103</v>
+      </c>
+      <c r="B70" t="s">
+        <v>4057</v>
+      </c>
+      <c r="C70" t="s">
+        <v>3971</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>4104</v>
+      </c>
+      <c r="B71" t="s">
+        <v>3999</v>
+      </c>
+      <c r="C71" t="s">
+        <v>3971</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>4105</v>
+      </c>
+      <c r="B72" t="s">
+        <v>4106</v>
+      </c>
+      <c r="C72" t="s">
+        <v>3971</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>4107</v>
+      </c>
+      <c r="B73" t="s">
+        <v>4108</v>
+      </c>
+      <c r="C73" t="s">
+        <v>3971</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>4109</v>
+      </c>
+      <c r="B74" t="s">
+        <v>4110</v>
+      </c>
+      <c r="C74" t="s">
+        <v>3971</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>4111</v>
+      </c>
+      <c r="B75" t="s">
+        <v>4112</v>
+      </c>
+      <c r="C75" t="s">
+        <v>3971</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>4113</v>
+      </c>
+      <c r="B76" t="s">
+        <v>4114</v>
+      </c>
+      <c r="C76" t="s">
+        <v>3971</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>4115</v>
+      </c>
+      <c r="B77" t="s">
+        <v>4116</v>
+      </c>
+      <c r="C77" t="s">
+        <v>3971</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>4117</v>
+      </c>
+      <c r="B78" t="s">
+        <v>4118</v>
+      </c>
+      <c r="C78" t="s">
         <v>3971</v>
       </c>
     </row>

--- a/05_Figures/HRvLR/F3_People/c_data/f3_people.xlsx
+++ b/05_Figures/HRvLR/F3_People/c_data/f3_people.xlsx
@@ -11886,25 +11886,25 @@
     <t>LR_S30</t>
   </si>
   <si>
-    <t>a95402d461edffdb1bfe52e24fa7f7f5</t>
+    <t>6ffd152613b6c596eb12f0ce1df71a5a</t>
   </si>
   <si>
     <t>03_Group_comparisons/HRvLR/05_Classification/02_Sets/c_data/set_classification.xlsx</t>
   </si>
   <si>
-    <t>b178395b3633ca781c3d08c789b73be2</t>
+    <t>30442b8bcced4ce54404b877cc0e3157</t>
   </si>
   <si>
     <t>03_Group_comparisons/HRvLR/05_Classification/03_Modules/c_data/module_classification.xlsx</t>
   </si>
   <si>
-    <t>40af5ef3d827e7eda16199768c84b50c</t>
+    <t>a10c56c0d5664ccb52a494c68381f97f</t>
   </si>
   <si>
     <t>associate</t>
   </si>
   <si>
-    <t>22366981c91de546cdab366e3b1baab4</t>
+    <t>5978f7ac7eb610d2fe7ef3d675e11d30</t>
   </si>
   <si>
     <t>continuous</t>
@@ -11913,7 +11913,7 @@
     <t>04_Continuous_no_group/01_Trait_Associations/01_Proteins/c_data/protein_trait_associations.xlsx</t>
   </si>
   <si>
-    <t>4c94a3c340f52458c17e5a5394bde99d</t>
+    <t>2a6f1e68ca8a78711559deee9c66c594</t>
   </si>
   <si>
     <t>corrected</t>

--- a/05_Figures/HRvLR/F3_People/c_data/f3_people.xlsx
+++ b/05_Figures/HRvLR/F3_People/c_data/f3_people.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11957" uniqueCount="4119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11930" uniqueCount="4102">
   <si>
     <t>sheet</t>
   </si>
@@ -303,7 +303,7 @@
     <t>best single feature per task</t>
   </si>
   <si>
-    <t>03_Group_comparisons/HRvLR/05_Classification/01_Proteins/c_data/protein_classification.xlsx</t>
+    <t>03_Group_comparisons/HRvLR/c_data/05_protein_classification.xlsx</t>
   </si>
   <si>
     <t>auc, counts</t>
@@ -318,7 +318,7 @@
     <t>group difference against continuous interaction</t>
   </si>
   <si>
-    <t>03_Group_comparisons/HRvLR/06_Trait_Associations/c_data/trait_associations.xlsx</t>
+    <t>03_Group_comparisons/HRvLR/c_data/06_trait_associations.xlsx</t>
   </si>
   <si>
     <t>group_difference; interaction</t>
@@ -11886,25 +11886,25 @@
     <t>LR_S30</t>
   </si>
   <si>
-    <t>6ffd152613b6c596eb12f0ce1df71a5a</t>
-  </si>
-  <si>
-    <t>03_Group_comparisons/HRvLR/05_Classification/02_Sets/c_data/set_classification.xlsx</t>
-  </si>
-  <si>
-    <t>30442b8bcced4ce54404b877cc0e3157</t>
-  </si>
-  <si>
-    <t>03_Group_comparisons/HRvLR/05_Classification/03_Modules/c_data/module_classification.xlsx</t>
-  </si>
-  <si>
-    <t>a10c56c0d5664ccb52a494c68381f97f</t>
+    <t>8e7d3ebda8f282f990041f57147e6c22</t>
+  </si>
+  <si>
+    <t>03_Group_comparisons/HRvLR/c_data/05_set_classification.xlsx</t>
+  </si>
+  <si>
+    <t>6e4e44c4a3eea5d36d7d745179b7b2be</t>
+  </si>
+  <si>
+    <t>03_Group_comparisons/HRvLR/c_data/05_module_classification.xlsx</t>
+  </si>
+  <si>
+    <t>c5cc9c745e611ef5293c4bd0c60c471f</t>
   </si>
   <si>
     <t>associate</t>
   </si>
   <si>
-    <t>5978f7ac7eb610d2fe7ef3d675e11d30</t>
+    <t>2c11488e27c0aa8173ac318124bb0ced</t>
   </si>
   <si>
     <t>continuous</t>
@@ -12036,138 +12036,105 @@
     <t>1.2.1</t>
   </si>
   <si>
-    <t>evaluate</t>
+    <t>farver</t>
+  </si>
+  <si>
+    <t>2.1.2</t>
+  </si>
+  <si>
+    <t>foreach</t>
+  </si>
+  <si>
+    <t>1.5.2</t>
+  </si>
+  <si>
+    <t>generics</t>
+  </si>
+  <si>
+    <t>0.1.4</t>
+  </si>
+  <si>
+    <t>GetoptLong</t>
+  </si>
+  <si>
+    <t>1.1.1</t>
+  </si>
+  <si>
+    <t>ggh4x</t>
+  </si>
+  <si>
+    <t>0.3.1</t>
+  </si>
+  <si>
+    <t>ggplot2</t>
+  </si>
+  <si>
+    <t>4.0.3</t>
+  </si>
+  <si>
+    <t>ggrepel</t>
+  </si>
+  <si>
+    <t>0.9.8</t>
+  </si>
+  <si>
+    <t>GlobalOptions</t>
+  </si>
+  <si>
+    <t>glue</t>
+  </si>
+  <si>
+    <t>1.8.1</t>
+  </si>
+  <si>
+    <t>gtable</t>
+  </si>
+  <si>
+    <t>0.3.6</t>
+  </si>
+  <si>
+    <t>here</t>
+  </si>
+  <si>
+    <t>1.0.2</t>
+  </si>
+  <si>
+    <t>hms</t>
+  </si>
+  <si>
+    <t>1.1.4</t>
+  </si>
+  <si>
+    <t>IRanges</t>
+  </si>
+  <si>
+    <t>2.46.0</t>
+  </si>
+  <si>
+    <t>iterators</t>
+  </si>
+  <si>
+    <t>1.0.14</t>
+  </si>
+  <si>
+    <t>labeling</t>
+  </si>
+  <si>
+    <t>0.4.3</t>
+  </si>
+  <si>
+    <t>lattice</t>
+  </si>
+  <si>
+    <t>0.22-9</t>
+  </si>
+  <si>
+    <t>lifecycle</t>
   </si>
   <si>
     <t>1.0.5</t>
   </si>
   <si>
-    <t>farver</t>
-  </si>
-  <si>
-    <t>2.1.2</t>
-  </si>
-  <si>
-    <t>fastmap</t>
-  </si>
-  <si>
-    <t>1.2.0</t>
-  </si>
-  <si>
-    <t>foreach</t>
-  </si>
-  <si>
-    <t>1.5.2</t>
-  </si>
-  <si>
-    <t>generics</t>
-  </si>
-  <si>
-    <t>0.1.4</t>
-  </si>
-  <si>
-    <t>GetoptLong</t>
-  </si>
-  <si>
-    <t>1.1.1</t>
-  </si>
-  <si>
-    <t>ggh4x</t>
-  </si>
-  <si>
-    <t>0.3.1</t>
-  </si>
-  <si>
-    <t>ggplot2</t>
-  </si>
-  <si>
-    <t>4.0.3</t>
-  </si>
-  <si>
-    <t>ggrepel</t>
-  </si>
-  <si>
-    <t>0.9.8</t>
-  </si>
-  <si>
-    <t>GlobalOptions</t>
-  </si>
-  <si>
-    <t>glue</t>
-  </si>
-  <si>
-    <t>1.8.1</t>
-  </si>
-  <si>
-    <t>gtable</t>
-  </si>
-  <si>
-    <t>0.3.6</t>
-  </si>
-  <si>
-    <t>here</t>
-  </si>
-  <si>
-    <t>1.0.2</t>
-  </si>
-  <si>
-    <t>hms</t>
-  </si>
-  <si>
-    <t>1.1.4</t>
-  </si>
-  <si>
-    <t>htmltools</t>
-  </si>
-  <si>
-    <t>0.5.9</t>
-  </si>
-  <si>
-    <t>htmlwidgets</t>
-  </si>
-  <si>
-    <t>1.6.4</t>
-  </si>
-  <si>
-    <t>IRanges</t>
-  </si>
-  <si>
-    <t>2.46.0</t>
-  </si>
-  <si>
-    <t>iterators</t>
-  </si>
-  <si>
-    <t>1.0.14</t>
-  </si>
-  <si>
-    <t>jsonlite</t>
-  </si>
-  <si>
-    <t>2.0.0</t>
-  </si>
-  <si>
-    <t>knitr</t>
-  </si>
-  <si>
-    <t>1.51</t>
-  </si>
-  <si>
-    <t>labeling</t>
-  </si>
-  <si>
-    <t>0.4.3</t>
-  </si>
-  <si>
-    <t>lattice</t>
-  </si>
-  <si>
-    <t>0.22-9</t>
-  </si>
-  <si>
-    <t>lifecycle</t>
-  </si>
-  <si>
     <t>magrittr</t>
   </si>
   <si>
@@ -12198,12 +12165,6 @@
     <t>3.1-169</t>
   </si>
   <si>
-    <t>otel</t>
-  </si>
-  <si>
-    <t>0.2.0</t>
-  </si>
-  <si>
     <t>patchwork</t>
   </si>
   <si>
@@ -12285,12 +12246,6 @@
     <t>CRAN (R 4.6.1)</t>
   </si>
   <si>
-    <t>rmarkdown</t>
-  </si>
-  <si>
-    <t>2.31</t>
-  </si>
-  <si>
     <t>rprojroot</t>
   </si>
   <si>
@@ -12379,12 +12334,6 @@
   </si>
   <si>
     <t>3.0.2</t>
-  </si>
-  <si>
-    <t>xfun</t>
-  </si>
-  <si>
-    <t>0.57</t>
   </si>
   <si>
     <t>yaml</t>
@@ -101925,7 +101874,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -102197,7 +102146,7 @@
         <v>4014</v>
       </c>
       <c r="B25" t="s">
-        <v>4015</v>
+        <v>4005</v>
       </c>
       <c r="C25" t="s">
         <v>3971</v>
@@ -102205,10 +102154,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
+        <v>4015</v>
+      </c>
+      <c r="B26" t="s">
         <v>4016</v>
-      </c>
-      <c r="B26" t="s">
-        <v>4017</v>
       </c>
       <c r="C26" t="s">
         <v>3971</v>
@@ -102216,10 +102165,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
+        <v>4017</v>
+      </c>
+      <c r="B27" t="s">
         <v>4018</v>
-      </c>
-      <c r="B27" t="s">
-        <v>4009</v>
       </c>
       <c r="C27" t="s">
         <v>3971</v>
@@ -102255,7 +102204,7 @@
         <v>4024</v>
       </c>
       <c r="C30" t="s">
-        <v>3971</v>
+        <v>3968</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -102299,7 +102248,7 @@
         <v>4032</v>
       </c>
       <c r="C34" t="s">
-        <v>3968</v>
+        <v>3971</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -102362,7 +102311,7 @@
         <v>4043</v>
       </c>
       <c r="B40" t="s">
-        <v>4001</v>
+        <v>4044</v>
       </c>
       <c r="C40" t="s">
         <v>3971</v>
@@ -102370,10 +102319,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>4044</v>
+        <v>4045</v>
       </c>
       <c r="B41" t="s">
-        <v>4045</v>
+        <v>4046</v>
       </c>
       <c r="C41" t="s">
         <v>3971</v>
@@ -102381,10 +102330,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>4046</v>
+        <v>4047</v>
       </c>
       <c r="B42" t="s">
-        <v>4047</v>
+        <v>4048</v>
       </c>
       <c r="C42" t="s">
         <v>3971</v>
@@ -102392,10 +102341,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>4048</v>
+        <v>4049</v>
       </c>
       <c r="B43" t="s">
-        <v>4049</v>
+        <v>4050</v>
       </c>
       <c r="C43" t="s">
         <v>3971</v>
@@ -102403,10 +102352,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>4050</v>
+        <v>4051</v>
       </c>
       <c r="B44" t="s">
-        <v>4051</v>
+        <v>4052</v>
       </c>
       <c r="C44" t="s">
         <v>3971</v>
@@ -102414,10 +102363,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>4052</v>
+        <v>4053</v>
       </c>
       <c r="B45" t="s">
-        <v>4053</v>
+        <v>4054</v>
       </c>
       <c r="C45" t="s">
         <v>3971</v>
@@ -102425,10 +102374,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>4054</v>
+        <v>4055</v>
       </c>
       <c r="B46" t="s">
-        <v>4055</v>
+        <v>4056</v>
       </c>
       <c r="C46" t="s">
         <v>3971</v>
@@ -102436,10 +102385,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>4056</v>
+        <v>4057</v>
       </c>
       <c r="B47" t="s">
-        <v>4057</v>
+        <v>4058</v>
       </c>
       <c r="C47" t="s">
         <v>3971</v>
@@ -102447,10 +102396,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>4058</v>
+        <v>4059</v>
       </c>
       <c r="B48" t="s">
-        <v>4059</v>
+        <v>4060</v>
       </c>
       <c r="C48" t="s">
         <v>3971</v>
@@ -102458,10 +102407,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>4060</v>
+        <v>4061</v>
       </c>
       <c r="B49" t="s">
-        <v>4061</v>
+        <v>4062</v>
       </c>
       <c r="C49" t="s">
         <v>3971</v>
@@ -102469,10 +102418,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>4062</v>
+        <v>4063</v>
       </c>
       <c r="B50" t="s">
-        <v>4063</v>
+        <v>4064</v>
       </c>
       <c r="C50" t="s">
         <v>3971</v>
@@ -102480,10 +102429,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="B51" t="s">
-        <v>4065</v>
+        <v>4066</v>
       </c>
       <c r="C51" t="s">
         <v>3971</v>
@@ -102491,21 +102440,21 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="B52" t="s">
-        <v>4067</v>
+        <v>4068</v>
       </c>
       <c r="C52" t="s">
-        <v>3971</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>4068</v>
+        <v>4070</v>
       </c>
       <c r="B53" t="s">
-        <v>4069</v>
+        <v>4071</v>
       </c>
       <c r="C53" t="s">
         <v>3971</v>
@@ -102513,21 +102462,21 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>4070</v>
+        <v>4072</v>
       </c>
       <c r="B54" t="s">
-        <v>4071</v>
+        <v>4073</v>
       </c>
       <c r="C54" t="s">
-        <v>3971</v>
+        <v>3968</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>4072</v>
+        <v>4074</v>
       </c>
       <c r="B55" t="s">
-        <v>4073</v>
+        <v>4075</v>
       </c>
       <c r="C55" t="s">
         <v>3971</v>
@@ -102535,10 +102484,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>4074</v>
+        <v>4076</v>
       </c>
       <c r="B56" t="s">
-        <v>4075</v>
+        <v>4077</v>
       </c>
       <c r="C56" t="s">
         <v>3971</v>
@@ -102546,10 +102495,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>4076</v>
+        <v>4078</v>
       </c>
       <c r="B57" t="s">
-        <v>4077</v>
+        <v>4079</v>
       </c>
       <c r="C57" t="s">
         <v>3971</v>
@@ -102557,10 +102506,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>4078</v>
+        <v>4080</v>
       </c>
       <c r="B58" t="s">
-        <v>4079</v>
+        <v>4081</v>
       </c>
       <c r="C58" t="s">
         <v>3971</v>
@@ -102568,21 +102517,21 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>4080</v>
+        <v>4082</v>
       </c>
       <c r="B59" t="s">
-        <v>4081</v>
+        <v>4083</v>
       </c>
       <c r="C59" t="s">
-        <v>4082</v>
+        <v>3971</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>4083</v>
+        <v>4084</v>
       </c>
       <c r="B60" t="s">
-        <v>4084</v>
+        <v>4085</v>
       </c>
       <c r="C60" t="s">
         <v>3971</v>
@@ -102590,10 +102539,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>4085</v>
+        <v>4086</v>
       </c>
       <c r="B61" t="s">
-        <v>4086</v>
+        <v>4087</v>
       </c>
       <c r="C61" t="s">
         <v>3971</v>
@@ -102601,13 +102550,13 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>4087</v>
+        <v>4088</v>
       </c>
       <c r="B62" t="s">
-        <v>4088</v>
+        <v>4044</v>
       </c>
       <c r="C62" t="s">
-        <v>3968</v>
+        <v>3971</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -102615,7 +102564,7 @@
         <v>4089</v>
       </c>
       <c r="B63" t="s">
-        <v>4090</v>
+        <v>3999</v>
       </c>
       <c r="C63" t="s">
         <v>3971</v>
@@ -102623,10 +102572,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
+        <v>4090</v>
+      </c>
+      <c r="B64" t="s">
         <v>4091</v>
-      </c>
-      <c r="B64" t="s">
-        <v>4092</v>
       </c>
       <c r="C64" t="s">
         <v>3971</v>
@@ -102634,10 +102583,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
+        <v>4092</v>
+      </c>
+      <c r="B65" t="s">
         <v>4093</v>
-      </c>
-      <c r="B65" t="s">
-        <v>4094</v>
       </c>
       <c r="C65" t="s">
         <v>3971</v>
@@ -102645,10 +102594,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
+        <v>4094</v>
+      </c>
+      <c r="B66" t="s">
         <v>4095</v>
-      </c>
-      <c r="B66" t="s">
-        <v>4096</v>
       </c>
       <c r="C66" t="s">
         <v>3971</v>
@@ -102656,10 +102605,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
+        <v>4096</v>
+      </c>
+      <c r="B67" t="s">
         <v>4097</v>
-      </c>
-      <c r="B67" t="s">
-        <v>4098</v>
       </c>
       <c r="C67" t="s">
         <v>3971</v>
@@ -102667,10 +102616,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
+        <v>4098</v>
+      </c>
+      <c r="B68" t="s">
         <v>4099</v>
-      </c>
-      <c r="B68" t="s">
-        <v>4100</v>
       </c>
       <c r="C68" t="s">
         <v>3971</v>
@@ -102678,111 +102627,12 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
+        <v>4100</v>
+      </c>
+      <c r="B69" t="s">
         <v>4101</v>
       </c>
-      <c r="B69" t="s">
-        <v>4102</v>
-      </c>
       <c r="C69" t="s">
-        <v>3971</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" t="s">
-        <v>4103</v>
-      </c>
-      <c r="B70" t="s">
-        <v>4057</v>
-      </c>
-      <c r="C70" t="s">
-        <v>3971</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71" t="s">
-        <v>4104</v>
-      </c>
-      <c r="B71" t="s">
-        <v>3999</v>
-      </c>
-      <c r="C71" t="s">
-        <v>3971</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72" t="s">
-        <v>4105</v>
-      </c>
-      <c r="B72" t="s">
-        <v>4106</v>
-      </c>
-      <c r="C72" t="s">
-        <v>3971</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" t="s">
-        <v>4107</v>
-      </c>
-      <c r="B73" t="s">
-        <v>4108</v>
-      </c>
-      <c r="C73" t="s">
-        <v>3971</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74" t="s">
-        <v>4109</v>
-      </c>
-      <c r="B74" t="s">
-        <v>4110</v>
-      </c>
-      <c r="C74" t="s">
-        <v>3971</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75" t="s">
-        <v>4111</v>
-      </c>
-      <c r="B75" t="s">
-        <v>4112</v>
-      </c>
-      <c r="C75" t="s">
-        <v>3971</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" t="s">
-        <v>4113</v>
-      </c>
-      <c r="B76" t="s">
-        <v>4114</v>
-      </c>
-      <c r="C76" t="s">
-        <v>3971</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77" t="s">
-        <v>4115</v>
-      </c>
-      <c r="B77" t="s">
-        <v>4116</v>
-      </c>
-      <c r="C77" t="s">
-        <v>3971</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78" t="s">
-        <v>4117</v>
-      </c>
-      <c r="B78" t="s">
-        <v>4118</v>
-      </c>
-      <c r="C78" t="s">
         <v>3971</v>
       </c>
     </row>

--- a/05_Figures/HRvLR/F3_People/c_data/f3_people.xlsx
+++ b/05_Figures/HRvLR/F3_People/c_data/f3_people.xlsx
@@ -45,7 +45,7 @@
     <t>panel_a</t>
   </si>
   <si>
-    <t>a: best feature per task and level: AUC, DeLong and bootstrap CIs, p, counts at p &lt; 0.05.</t>
+    <t>a: best feature per task and feature type: AUC, DeLong and bootstrap CIs, p, n at p &lt; 0.05.</t>
   </si>
   <si>
     <t>panel_b</t>
@@ -111,10 +111,10 @@
     <t>Rule that picks the panel's rows.</t>
   </si>
   <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>Feature level: proteins, sets or modules.</t>
+    <t>feature_type</t>
+  </si>
+  <si>
+    <t>Feature type: proteins, sets or modules.</t>
   </si>
   <si>
     <t>task</t>
@@ -255,10 +255,10 @@
     <t>Phenotype trait: pct_ = percent change over training; fcsa = fibre cross-sectional area (mixed, type I, type II), mcsa = muscle cross-sectional area, leg_press/leg_ext_1rm = one-repetition maximum, comp_hypertrophy = composite hypertrophy score, volume_load_total_kg = training volume.</t>
   </si>
   <si>
-    <t>arm</t>
-  </si>
-  <si>
-    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster grouping.</t>
+    <t>group</t>
+  </si>
+  <si>
+    <t>Group the row belongs to: HR or LR, or C1 or C2 in a proteome grouping.</t>
   </si>
   <si>
     <t>input</t>
@@ -309,7 +309,7 @@
     <t>auc, counts</t>
   </si>
   <si>
-    <t>smallest p per task and level, then AUC furthest from 0.5</t>
+    <t>smallest p per task and feature type, then AUC furthest from 0.5</t>
   </si>
   <si>
     <t>b</t>
@@ -11886,25 +11886,25 @@
     <t>LR_S30</t>
   </si>
   <si>
-    <t>8e7d3ebda8f282f990041f57147e6c22</t>
+    <t>43cd77e75ace3549f8ced7c5f3e61728</t>
   </si>
   <si>
     <t>03_Group_comparisons/HRvLR/c_data/05_set_classification.xlsx</t>
   </si>
   <si>
-    <t>6e4e44c4a3eea5d36d7d745179b7b2be</t>
+    <t>36ca0525abc0f23a4da4eba41e1c7b3d</t>
   </si>
   <si>
     <t>03_Group_comparisons/HRvLR/c_data/05_module_classification.xlsx</t>
   </si>
   <si>
-    <t>c5cc9c745e611ef5293c4bd0c60c471f</t>
+    <t>744868e310d91bf0b54ca41e150da133</t>
   </si>
   <si>
     <t>associate</t>
   </si>
   <si>
-    <t>2c11488e27c0aa8173ac318124bb0ced</t>
+    <t>c8706864101e818ac01fce9b392de7bc</t>
   </si>
   <si>
     <t>continuous</t>
@@ -11913,7 +11913,7 @@
     <t>04_Continuous_no_group/01_Trait_Associations/01_Proteins/c_data/protein_trait_associations.xlsx</t>
   </si>
   <si>
-    <t>2a6f1e68ca8a78711559deee9c66c594</t>
+    <t>a8ae16fa51127b014307f106751cdd89</t>
   </si>
   <si>
     <t>corrected</t>
@@ -11922,7 +11922,7 @@
     <t>01_Processing/03_Quantification/c_data/DAList_corrected.rds</t>
   </si>
   <si>
-    <t>4b7147a39661ba7f9ed17b81a9ef9a9b</t>
+    <t>44029c7b54c5cc454b37546acd46c065</t>
   </si>
   <si>
     <t>phenotype</t>
@@ -11931,7 +11931,7 @@
     <t>00_Setup/Input/phenotype.csv</t>
   </si>
   <si>
-    <t>5a1989db406daa0b70189a9f0df52cf3</t>
+    <t>cdb8d908fb24ab0d2be6f2d00021db81</t>
   </si>
   <si>
     <t>BiocGenerics</t>
